--- a/data/list_of_member_companies/0087.xlsx
+++ b/data/list_of_member_companies/0087.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ivpf201v.takamatsu.local\Profile\t10202\Desktop\オープンデータデジタル戦略課\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFDFB8CC-1AD1-48B2-8739-4660607F2750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0087" sheetId="1" r:id="rId1"/>
@@ -27,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="303">
   <si>
     <t>#property</t>
   </si>
@@ -961,18 +967,32 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
+    <t>7/09/2025</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
     <t>ロボフィス株式会社</t>
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>7/14/2025</t>
+    <t>ＫＢＮ株式会社</t>
+  </si>
+  <si>
+    <t>株式会社ケーブルメディア四国</t>
+  </si>
+  <si>
+    <t>11/25/2025</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>11/26/2025</t>
     <phoneticPr fontId="18"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1883,8 +1903,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C158"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C160"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="50.25" bestFit="1" customWidth="1"/>
@@ -3622,15 +3642,36 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
+        <v>298</v>
+      </c>
+      <c r="C158" t="s">
         <v>297</v>
       </c>
-      <c r="C158" t="s">
-        <v>298</v>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A159">
+        <v>158</v>
+      </c>
+      <c r="B159" t="s">
+        <v>299</v>
+      </c>
+      <c r="C159" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A160">
+        <v>159</v>
+      </c>
+      <c r="B160" t="s">
+        <v>300</v>
+      </c>
+      <c r="C160" t="s">
+        <v>302</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>